--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487882_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487882_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4862</v>
+        <v>5.818</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8338</v>
+        <v>6.0481</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3476</v>
+        <v>-0.2301</v>
       </c>
       <c r="G2" t="n">
         <v>3.4702</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5708</v>
+        <v>-0.2391</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0164</v>
+        <v>0.1338</v>
       </c>
       <c r="V2" t="n">
         <v>2.795</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2174</v>
+        <v>3.915</v>
       </c>
       <c r="E3" t="n">
-        <v>1.944</v>
+        <v>1.7297</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2734</v>
+        <v>2.1853</v>
       </c>
       <c r="G3" t="n">
         <v>3.5778</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7614</v>
+        <v>0.459</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1272</v>
+        <v>-0.0871</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6342</v>
+        <v>0.5461</v>
       </c>
       <c r="V3" t="n">
         <v>1.7513</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5425</v>
+        <v>3.3106</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9341</v>
+        <v>0.2911</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6084</v>
+        <v>3.0195</v>
       </c>
       <c r="G4" t="n">
         <v>0.1659</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9603</v>
+        <v>0.7284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.972</v>
+        <v>0.3291</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0117</v>
+        <v>0.3993</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0588</v>
+        <v>2.5155</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2523</v>
+        <v>-0.3367</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3111</v>
+        <v>2.8522</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6327</v>
+        <v>1.1495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9789</v>
+        <v>-0.9617</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3462</v>
+        <v>2.1113</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5592</v>
+        <v>-0.0057</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07679999999999999</v>
+        <v>-1.721</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.636</v>
+        <v>1.7153</v>
       </c>
       <c r="M5" t="n">
-        <v>1.192</v>
+        <v>1.1552</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9021</v>
+        <v>0.7592</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2898</v>
+        <v>0.396</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8673</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>-0.331</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5197</v>
+        <v>0.2401</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2737</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9885</v>
+        <v>1.2952</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6581</v>
+        <v>1.2395</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6466</v>
+        <v>0.0557</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1495</v>
+        <v>0.8397</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9617</v>
+        <v>-0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1113</v>
+        <v>0.8801</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0057</v>
+        <v>1.7134</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.721</v>
+        <v>0.3026</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7153</v>
+        <v>1.4108</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1552</v>
+        <v>-0.8737</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7592</v>
+        <v>-0.3431</v>
       </c>
       <c r="O6" t="n">
-        <v>0.396</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>1.4568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6178</v>
+        <v>-0.3114</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6524</v>
+        <v>-0.2657</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0346</v>
+        <v>-0.0456</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7683</v>
+        <v>1.0987</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9181</v>
+        <v>-0.038</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1498</v>
+        <v>1.1367</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8397</v>
+        <v>0.6327</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0404</v>
+        <v>0.9789</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8801</v>
+        <v>-0.3462</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7134</v>
+        <v>-0.5592</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3026</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4108</v>
+        <v>-0.636</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8737</v>
+        <v>1.192</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3431</v>
+        <v>0.9021</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.2898</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.2081</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8383</v>
+        <v>0.9072</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.4381</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2511</v>
+        <v>1.3453</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6899</v>
+        <v>-1.2737</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6899</v>
+        <v>-2.4412</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5949</v>
+        <v>0.9869</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9838</v>
+        <v>-2.0909</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5787</v>
+        <v>3.0778</v>
       </c>
       <c r="G8" t="n">
         <v>0.5238</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0339</v>
+        <v>0.358</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0959</v>
+        <v>0.4032</v>
       </c>
       <c r="V8" t="n">
         <v>0.9376</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8343</v>
+        <v>-0.7831</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9906</v>
+        <v>-1.6637</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1563</v>
+        <v>0.8806</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6569</v>
+        <v>-0.5626</v>
       </c>
       <c r="H9" t="n">
-        <v>0.194</v>
+        <v>-0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4629</v>
+        <v>-0.5372</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5631</v>
+        <v>0.107</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1815</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7446</v>
+        <v>0.0302</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.6696</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3755</v>
+        <v>-0.1022</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2817</v>
+        <v>-0.5674</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4443</v>
+        <v>-0.4286</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1924</v>
+        <v>-0.5219</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2519</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>D. ROLLINS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9006</v>
+        <v>-1.4323</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6637</v>
+        <v>-0.0643</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7631</v>
+        <v>-1.3681</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5626</v>
+        <v>1.4271</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0254</v>
+        <v>0.2261</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5372</v>
+        <v>1.201</v>
       </c>
       <c r="J10" t="n">
-        <v>0.107</v>
+        <v>1.1658</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0302</v>
+        <v>1.1275</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6696</v>
+        <v>0.2612</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1022</v>
+        <v>0.1877</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5674</v>
+        <v>0.0735</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.2487</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5461</v>
+        <v>-0.0675</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5219</v>
+        <v>0.0186</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0241</v>
+        <v>-0.0861</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ROLLINS</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8522</v>
+        <v>-1.5565</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2786</v>
+        <v>-2.4193</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5736</v>
+        <v>0.8627</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4271</v>
+        <v>0.6569</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2261</v>
+        <v>0.194</v>
       </c>
       <c r="I11" t="n">
-        <v>1.201</v>
+        <v>0.4629</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1658</v>
+        <v>0.5631</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0384</v>
+        <v>-0.1815</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1275</v>
+        <v>0.7446</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2612</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1877</v>
+        <v>0.3755</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0735</v>
+        <v>-0.2817</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2487</v>
+        <v>-3.3299</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4873</v>
+        <v>-0.2779</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1957</v>
+        <v>-0.2362</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2916</v>
+        <v>-0.0417</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7513</v>
+        <v>0.3538</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.2944</v>
+        <v>-9.3927</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.9839</v>
+        <v>-8.876799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3104</v>
+        <v>-0.5159</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5328</v>
@@ -1390,13 +1390,13 @@
         <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4723</v>
+        <v>-0.5707</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7829</v>
+        <v>-0.6758</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3106</v>
+        <v>0.1051</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.775099999999998</v>
+        <v>5.7753</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.181000000000001</v>
+        <v>-6.181299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9562</v>
+        <v>11.9564</v>
       </c>
       <c r="G13" t="n">
         <v>7.3482</v>
@@ -1438,7 +1438,7 @@
         <v>1.4497</v>
       </c>
       <c r="I13" t="n">
-        <v>5.8987</v>
+        <v>5.898700000000001</v>
       </c>
       <c r="J13" t="n">
         <v>5.042800000000001</v>
@@ -1450,13 +1450,13 @@
         <v>7.102999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3056</v>
+        <v>2.305600000000001</v>
       </c>
       <c r="N13" t="n">
         <v>3.5095</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2042</v>
+        <v>-1.204199999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-4.1625</v>
@@ -1468,16 +1468,16 @@
         <v>13.5275</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4667999999999996</v>
+        <v>0.4665999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-2.6262</v>
       </c>
       <c r="U13" t="n">
-        <v>3.093</v>
+        <v>3.0928</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1228</v>
+        <v>2.122800000000001</v>
       </c>
       <c r="W13" t="n">
         <v>9.092600000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8681</v>
+        <v>4.2688</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0052</v>
+        <v>4.1124</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1372</v>
+        <v>0.1564</v>
       </c>
       <c r="G14" t="n">
         <v>1.5487</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0157</v>
+        <v>0.3851</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0386</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0529</v>
+        <v>0.3464</v>
       </c>
       <c r="V14" t="n">
         <v>2.3351</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5641</v>
+        <v>2.2458</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1552</v>
+        <v>1.3036</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4088</v>
+        <v>0.9421</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3914</v>
+        <v>0.8932</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7376</v>
+        <v>0.9617</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3462</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3264</v>
+        <v>1.2076</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4643</v>
+        <v>0.921</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8621</v>
+        <v>0.2865</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.3144</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2733</v>
+        <v>0.0407</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2083</v>
+        <v>-0.3551</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4974</v>
+        <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.464</v>
+        <v>-0.7098</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4501</v>
+        <v>-0.7177</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0139</v>
+        <v>0.0078</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7076</v>
+        <v>0.8137</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4599</v>
+        <v>0.8137</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0696</v>
+        <v>1.5796</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3036</v>
+        <v>0.7724</v>
       </c>
       <c r="F16" t="n">
-        <v>0.766</v>
+        <v>0.8072</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8932</v>
+        <v>1.46</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9617</v>
+        <v>0.0493</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.06859999999999999</v>
+        <v>1.4108</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2076</v>
+        <v>1.9296</v>
       </c>
       <c r="K16" t="n">
-        <v>0.921</v>
+        <v>0.0576</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2865</v>
+        <v>1.872</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3144</v>
+        <v>-0.4696</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0407</v>
+        <v>-0.0083</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3551</v>
+        <v>-0.4613</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.886</v>
+        <v>0.1195</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7177</v>
+        <v>-0.1167</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1683</v>
+        <v>0.2362</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9264</v>
+        <v>1.5776</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2366</v>
+        <v>0.7266</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6898</v>
+        <v>0.851</v>
       </c>
       <c r="G17" t="n">
-        <v>1.46</v>
+        <v>1.3914</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0493</v>
+        <v>1.7376</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4108</v>
+        <v>-0.3462</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9296</v>
+        <v>2.3264</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0576</v>
+        <v>1.4643</v>
       </c>
       <c r="L17" t="n">
-        <v>1.872</v>
+        <v>0.8621</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4696</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0083</v>
+        <v>0.2733</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4613</v>
+        <v>-1.2083</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>2.4974</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5337</v>
+        <v>0.4776</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6524</v>
+        <v>0.0215</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1188</v>
+        <v>0.4561</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4782</v>
+        <v>0.596</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.4504</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5695</v>
+        <v>1.0464</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1331</v>
+        <v>-1.4901</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.049</v>
+        <v>-0.2728</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1821</v>
+        <v>-1.2173</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0392</v>
+        <v>-0.6082</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.5992</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0392</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0939</v>
+        <v>-0.8818</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.049</v>
+        <v>0.3265</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1429</v>
+        <v>-1.2083</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2081</v>
+        <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.137</v>
+        <v>-0.3301</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1305</v>
+        <v>-0.199</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2675</v>
+        <v>-0.1311</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3318</v>
+        <v>0.4973</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4504</v>
+        <v>0.0159</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7822</v>
+        <v>0.4814</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4901</v>
+        <v>0.1331</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2728</v>
+        <v>-0.049</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2173</v>
+        <v>0.1821</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6082</v>
+        <v>0.0392</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5992</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0392</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8818</v>
+        <v>0.0939</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3265</v>
+        <v>-0.049</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2083</v>
+        <v>0.1429</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5944</v>
+        <v>0.1561</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.199</v>
+        <v>-0.0233</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3953</v>
+        <v>0.1794</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1031</v>
+        <v>-0.1634</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.115</v>
+        <v>0.2065</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0119</v>
+        <v>-0.3698</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5727</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.659</v>
+        <v>0.5988</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0504</v>
+        <v>0.6687</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8137</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3611</v>
+        <v>-2.4363</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8189</v>
+        <v>-3.3065</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5422</v>
+        <v>0.8702</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3926</v>
+        <v>-2.6057</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6506</v>
+        <v>0.1024</v>
       </c>
       <c r="I21" t="n">
-        <v>0.258</v>
+        <v>-2.7081</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7599</v>
+        <v>-1.985</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.8383</v>
+        <v>-1.1261</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0784</v>
+        <v>-0.8589</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3674</v>
+        <v>-0.6206</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1877</v>
+        <v>1.2286</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1796</v>
+        <v>-1.8492</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0406</v>
+        <v>2.7055</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>2.7055</v>
       </c>
       <c r="S21" t="n">
-        <v>1.096</v>
+        <v>-0.4311</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7111</v>
+        <v>-0.6138</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3849</v>
+        <v>0.1827</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1051</v>
       </c>
       <c r="W21" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3351</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6903</v>
+        <v>-3.0231</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4136</v>
+        <v>-2.569</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7234</v>
+        <v>-0.4541</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6057</v>
+        <v>-2.3926</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1024</v>
+        <v>-2.6506</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7081</v>
+        <v>0.258</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.985</v>
+        <v>-2.7599</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1261</v>
+        <v>-2.8383</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8589</v>
+        <v>0.0784</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6206</v>
+        <v>0.3674</v>
       </c>
       <c r="N22" t="n">
-        <v>1.2286</v>
+        <v>0.1877</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8492</v>
+        <v>0.1796</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6851</v>
+        <v>0.434</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.721</v>
+        <v>-0.039</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0359</v>
+        <v>0.473</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1051</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.612</v>
+        <v>-5.0803</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2713</v>
+        <v>-5.5928</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6593</v>
+        <v>0.5125</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1699</v>
@@ -2248,13 +2248,13 @@
         <v>2.4974</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1507</v>
+        <v>-0.619</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.46</v>
+        <v>-0.7815</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3093</v>
+        <v>0.1625</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7076</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2468</v>
+        <v>-5.8373</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.4965</v>
+        <v>-7.1751</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2497</v>
+        <v>1.3378</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5436</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9571</v>
+        <v>-0.5475</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9134</v>
+        <v>-0.5919</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0437</v>
+        <v>0.0444</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7751</v>
+        <v>-5.775300000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-11.9564</v>
       </c>
       <c r="F25" t="n">
-        <v>6.1812</v>
+        <v>6.181100000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-7.3482</v>
@@ -2374,7 +2374,7 @@
         <v>-1.4496</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.8987</v>
+        <v>-5.898700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>-2.305500000000001</v>
@@ -2383,7 +2383,7 @@
         <v>-3.5095</v>
       </c>
       <c r="L25" t="n">
-        <v>1.204</v>
+        <v>1.204000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-5.0425</v>
@@ -2395,7 +2395,7 @@
         <v>-7.1028</v>
       </c>
       <c r="P25" t="n">
-        <v>4.162299999999999</v>
+        <v>4.162299999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.5277</v>
@@ -2404,13 +2404,13 @@
         <v>17.69</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4666999999999999</v>
+        <v>-0.4664</v>
       </c>
       <c r="T25" t="n">
         <v>-3.0928</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6263</v>
+        <v>2.6261</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1228</v>
@@ -2419,7 +2419,7 @@
         <v>6.9697</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.092599999999999</v>
+        <v>-9.092600000000001</v>
       </c>
     </row>
   </sheetData>
